--- a/ConfigWorkspace/Data/projectile.xlsx
+++ b/ConfigWorkspace/Data/projectile.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -50,9 +50,6 @@
     <t>min_throw_distance</t>
   </si>
   <si>
-    <t>tile_state</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>float!#range=[0.01,5]</t>
   </si>
   <si>
-    <t>TileStateType</t>
-  </si>
-  <si>
     <t>ElementType</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>最小投掷距离（世界单位）</t>
   </si>
   <si>
-    <t>落地后目标格转成的状态（Normal=不改）</t>
-  </si>
-  <si>
     <t>类型</t>
   </si>
   <si>
@@ -155,9 +146,6 @@
     <t>纯水</t>
   </si>
   <si>
-    <t>泥浆</t>
-  </si>
-  <si>
     <t>水</t>
   </si>
   <si>
@@ -167,9 +155,6 @@
     <t>热水</t>
   </si>
   <si>
-    <t>常规</t>
-  </si>
-  <si>
     <t>冷水</t>
   </si>
   <si>
@@ -185,10 +170,13 @@
     <t>湿土</t>
   </si>
   <si>
-    <t>沙土</t>
+    <t>沙</t>
   </si>
   <si>
     <t>含沙</t>
+  </si>
+  <si>
+    <t>粘土</t>
   </si>
   <si>
     <t>冰种子</t>
@@ -1179,10 +1167,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1204,7 +1192,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1219,139 +1207,127 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="1" t="s">
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="B3" t="s">
         <v>25</v>
       </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>27</v>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="1" t="s">
+    <row r="5" spans="2:12">
+      <c r="B5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>0.6</v>
@@ -1365,31 +1341,28 @@
       <c r="G5">
         <v>0.4</v>
       </c>
-      <c r="H5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>43</v>
+      <c r="H5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" s="2">
-        <v>3</v>
-      </c>
-      <c r="L5" s="2">
         <v>1</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>44</v>
+      <c r="L5" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:12">
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -1403,31 +1376,28 @@
       <c r="G6">
         <v>0.4</v>
       </c>
-      <c r="H6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>43</v>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="2">
+        <v>3</v>
       </c>
       <c r="J6" s="2">
         <v>3</v>
       </c>
       <c r="K6" s="2">
-        <v>3</v>
-      </c>
-      <c r="L6" s="2">
         <v>1</v>
       </c>
-      <c r="M6" s="1" t="s">
-        <v>44</v>
+      <c r="L6" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:12">
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D7">
         <v>0.6</v>
@@ -1441,31 +1411,28 @@
       <c r="G7">
         <v>0.4</v>
       </c>
-      <c r="H7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="2">
+        <v>-2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="2">
-        <v>-2</v>
-      </c>
-      <c r="K7" s="2">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D8">
         <v>0.6</v>
@@ -1479,11 +1446,11 @@
       <c r="G8">
         <v>0.4</v>
       </c>
-      <c r="H8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>49</v>
+      <c r="H8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
@@ -1491,19 +1458,16 @@
       <c r="K8" s="2">
         <v>0</v>
       </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>50</v>
+      <c r="L8" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:12">
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D9">
         <v>0.6</v>
@@ -1517,31 +1481,28 @@
       <c r="G9">
         <v>0.4</v>
       </c>
-      <c r="H9" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>49</v>
+      <c r="H9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
       </c>
       <c r="J9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" s="2">
-        <v>2</v>
-      </c>
-      <c r="L9" s="2">
         <v>1</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>50</v>
+      <c r="L9" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:12">
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D10">
         <v>0.6</v>
@@ -1555,31 +1516,28 @@
       <c r="G10">
         <v>0.4</v>
       </c>
-      <c r="H10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>49</v>
+      <c r="H10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
       </c>
       <c r="J10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2">
         <v>0</v>
       </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>53</v>
+      <c r="L10" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:12">
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D11">
         <v>0.6</v>
@@ -1593,31 +1551,28 @@
       <c r="G11">
         <v>0.4</v>
       </c>
-      <c r="H11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>55</v>
+      <c r="H11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
       </c>
       <c r="J11" s="2">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2">
         <v>0</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>44</v>
+      <c r="L11" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:12">
       <c r="B12" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D12">
         <v>0.6</v>
@@ -1631,31 +1586,28 @@
       <c r="G12">
         <v>0.4</v>
       </c>
-      <c r="H12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>55</v>
+      <c r="H12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="2">
+        <v>-4</v>
       </c>
       <c r="J12" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
       </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>44</v>
+      <c r="L12" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:12">
       <c r="B13" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>0.6</v>
@@ -1669,31 +1621,28 @@
       <c r="G13">
         <v>0.4</v>
       </c>
-      <c r="H13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>55</v>
+      <c r="H13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="2">
+        <v>4</v>
       </c>
       <c r="J13" s="2">
         <v>0</v>
       </c>
       <c r="K13" s="2">
-        <v>2</v>
-      </c>
-      <c r="L13" s="2">
         <v>0</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>58</v>
+      <c r="L13" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:12">
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -1707,23 +1656,55 @@
       <c r="G14">
         <v>0.4</v>
       </c>
-      <c r="H14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>55</v>
+      <c r="H14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L14" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15">
+        <v>0.6</v>
+      </c>
+      <c r="E15">
         <v>2</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>44</v>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>0.4</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/projectile.xlsx
+++ b/ConfigWorkspace/Data/projectile.xlsx
@@ -1167,10 +1167,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1180,35 +1180,23 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1218,35 +1206,23 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1256,35 +1232,23 @@
       <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1294,416 +1258,272 @@
       <c r="C4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
+      <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="2:8">
       <c r="B5" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D5">
-        <v>0.6</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>0.4</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="K5" s="2">
+      <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="2:8">
       <c r="B6" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D6">
-        <v>0.6</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>0.4</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="2">
+      <c r="E6" s="2">
         <v>3</v>
       </c>
-      <c r="J6" s="2">
+      <c r="F6" s="2">
         <v>3</v>
       </c>
-      <c r="K6" s="2">
+      <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="2:8">
       <c r="B7" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D7">
-        <v>0.6</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>0.4</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I7" s="2">
+      <c r="E7" s="2">
         <v>-2</v>
       </c>
-      <c r="J7" s="2">
+      <c r="F7" s="2">
         <v>3</v>
       </c>
-      <c r="K7" s="2">
+      <c r="G7" s="2">
         <v>1</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:8">
       <c r="B8" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D8">
-        <v>0.6</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8">
-        <v>0.4</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1" t="s">
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:8">
       <c r="B9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D9">
-        <v>0.6</v>
-      </c>
-      <c r="E9">
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
         <v>2</v>
       </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9">
-        <v>0.4</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <v>2</v>
-      </c>
-      <c r="K9" s="2">
+      <c r="G9" s="2">
         <v>1</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10" spans="2:8">
       <c r="B10" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D10">
-        <v>0.6</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10">
-        <v>0.4</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="2">
+      <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1" t="s">
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="2:12">
+    <row r="11" spans="2:8">
       <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D11">
-        <v>0.6</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <v>0.4</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1" t="s">
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12" spans="2:8">
       <c r="B12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D12">
-        <v>0.6</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>5</v>
-      </c>
-      <c r="G12">
-        <v>0.4</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I12" s="2">
+      <c r="E12" s="2">
         <v>-4</v>
       </c>
-      <c r="J12" s="2">
+      <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c r="K12" s="2">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1" t="s">
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:8">
       <c r="B13" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D13">
-        <v>0.6</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>5</v>
-      </c>
-      <c r="G13">
-        <v>0.4</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="2">
+      <c r="E13" s="2">
         <v>4</v>
       </c>
-      <c r="J13" s="2">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1" t="s">
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:8">
       <c r="B14" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D14">
-        <v>0.6</v>
-      </c>
-      <c r="E14">
+      <c r="D14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
         <v>2</v>
       </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-      <c r="G14">
-        <v>0.4</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
-        <v>2</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1" t="s">
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:8">
       <c r="B15" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D15">
-        <v>0.6</v>
-      </c>
-      <c r="E15">
+      <c r="D15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
         <v>2</v>
       </c>
-      <c r="F15">
-        <v>5</v>
-      </c>
-      <c r="G15">
-        <v>0.4</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2">
-        <v>2</v>
-      </c>
-      <c r="L15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>40</v>
       </c>
     </row>

--- a/ConfigWorkspace/Data/projectile.xlsx
+++ b/ConfigWorkspace/Data/projectile.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,6 @@
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,11 +466,6 @@
           <t>string!</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ElementType</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,11 +483,6 @@
           <t>c</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -515,11 +500,6 @@
           <t>显示名</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="E5" t="inlineStr">
@@ -532,11 +512,6 @@
           <t>纯水</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="E6" t="inlineStr">
@@ -547,11 +522,6 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>纯土</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Earth</t>
         </is>
       </c>
     </row>

--- a/ConfigWorkspace/Data/projectile.xlsx
+++ b/ConfigWorkspace/Data/projectile.xlsx
@@ -1,45 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C7E466-B657-4C02-B85C-558BAB8E1B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5670" yWindow="5535" windowWidth="28800" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>BallType</t>
+  </si>
+  <si>
+    <t>string!</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>球种ID</t>
+  </si>
+  <si>
+    <t>显示名</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>纯水</t>
+  </si>
+  <si>
+    <t>Earth</t>
+  </si>
+  <si>
+    <t>纯土</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -57,87 +111,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -425,107 +414,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>BallType</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string!</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>球种ID</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>显示名</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>纯水</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Earth</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>纯土</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>